--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20221.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="103">
   <si>
     <t>Mat</t>
   </si>
@@ -118,15 +118,6 @@
     <t>VELAZQUEZ</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>DIAZ</t>
   </si>
   <si>
@@ -139,9 +130,6 @@
     <t>SOLANO</t>
   </si>
   <si>
-    <t>VEGA</t>
-  </si>
-  <si>
     <t>APALE</t>
   </si>
   <si>
@@ -166,36 +154,6 @@
     <t>LARRACILLA</t>
   </si>
   <si>
-    <t>ARZATE</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>TENORIO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
     <t>ROJAS</t>
   </si>
   <si>
@@ -229,9 +187,6 @@
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
     <t>ZEPACTLE</t>
   </si>
   <si>
@@ -244,9 +199,6 @@
     <t>MALDONADO</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
     <t>MONGE</t>
   </si>
   <si>
@@ -268,24 +220,6 @@
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
     <t>ANGUIANO</t>
   </si>
   <si>
@@ -322,21 +256,9 @@
     <t>JOSE MIGUEL</t>
   </si>
   <si>
-    <t>TOBIAS</t>
-  </si>
-  <si>
-    <t>ESTEFANY CELESTE</t>
-  </si>
-  <si>
-    <t>ABIGAIL ANTONIA</t>
-  </si>
-  <si>
     <t>ABRIL</t>
   </si>
   <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
     <t>GUSTAVO KALEL</t>
   </si>
   <si>
@@ -346,9 +268,6 @@
     <t>KEVIN</t>
   </si>
   <si>
-    <t>NERY JOSELYN</t>
-  </si>
-  <si>
     <t>YULIET</t>
   </si>
   <si>
@@ -386,39 +305,6 @@
   </si>
   <si>
     <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>LUCIANA</t>
-  </si>
-  <si>
-    <t>DARA NAOMI</t>
-  </si>
-  <si>
-    <t>DANNA ANGELA</t>
-  </si>
-  <si>
-    <t>ILSE MARIA</t>
-  </si>
-  <si>
-    <t>JOSELYN</t>
-  </si>
-  <si>
-    <t>ZURI GABRIELA</t>
-  </si>
-  <si>
-    <t>ODALIS SOFIA</t>
-  </si>
-  <si>
-    <t>JESUS ADRIAN</t>
-  </si>
-  <si>
-    <t>ORESTES</t>
-  </si>
-  <si>
-    <t>MELISA VIANNEY</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
   </si>
   <si>
     <t>AMISADAI</t>
@@ -944,19 +830,19 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="G6">
-        <v>34.88</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1182,7 +1068,7 @@
         <v>43</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1414,19 +1300,19 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="G6">
-        <v>34.88</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1514,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1552,10 +1438,10 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1575,10 +1461,10 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1598,10 +1484,10 @@
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1621,10 +1507,10 @@
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1644,10 +1530,10 @@
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1670,7 +1556,7 @@
         <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1693,7 +1579,7 @@
         <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1713,10 +1599,10 @@
         <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1736,10 +1622,10 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1753,16 +1639,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920124</v>
+        <v>22330051920131</v>
       </c>
       <c r="B11" t="s">
         <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1776,16 +1662,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920126</v>
+        <v>22330051920346</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1799,16 +1685,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920130</v>
+        <v>22330051920247</v>
       </c>
       <c r="B13" t="s">
         <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1822,16 +1708,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920131</v>
+        <v>22330051920354</v>
       </c>
       <c r="B14" t="s">
         <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1845,22 +1731,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920132</v>
+        <v>21330051920303</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1868,22 +1754,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920346</v>
+        <v>21330051920316</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1891,137 +1777,137 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920247</v>
+        <v>22330051920003</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920354</v>
+        <v>22330051920320</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920258</v>
+        <v>22330051920321</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="D19" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920303</v>
+        <v>22330051920039</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920316</v>
+        <v>22330051920046</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="D21" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920003</v>
+        <v>22330051920053</v>
       </c>
       <c r="B22" t="s">
         <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="D22" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -2029,22 +1915,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920320</v>
+        <v>22330051920054</v>
       </c>
       <c r="B23" t="s">
         <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="D23" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -2052,22 +1938,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920321</v>
+        <v>22330051920064</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="D24" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -2075,22 +1961,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920039</v>
+        <v>22330051920066</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="D25" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -2098,22 +1984,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920046</v>
+        <v>22330051920336</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D26" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2121,22 +2007,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920053</v>
+        <v>22330051920340</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D27" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2144,22 +2030,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920054</v>
+        <v>22330051920172</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
         <v>67</v>
       </c>
       <c r="D28" t="s">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -2167,22 +2053,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920064</v>
+        <v>21330051920298</v>
       </c>
       <c r="B29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" t="s">
         <v>30</v>
       </c>
-      <c r="C29" t="s">
-        <v>80</v>
-      </c>
       <c r="D29" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -2190,22 +2076,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920066</v>
+        <v>21330051920299</v>
       </c>
       <c r="B30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" t="s">
         <v>30</v>
       </c>
-      <c r="C30" t="s">
-        <v>69</v>
-      </c>
       <c r="D30" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E30" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F30" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -2213,22 +2099,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>22330051920336</v>
+        <v>21330051920337</v>
       </c>
       <c r="B31" t="s">
         <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="D31" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="E31" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2236,22 +2122,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>22330051920340</v>
+        <v>20330051920235</v>
       </c>
       <c r="B32" t="s">
         <v>48</v>
       </c>
       <c r="C32" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="D32" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="E32" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2259,22 +2145,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>22330051920343</v>
+        <v>21330051920321</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="D33" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="E33" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2282,22 +2168,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>22330051920344</v>
+        <v>21330051920326</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="D34" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="E34" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F34" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -2305,392 +2191,24 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>22330051920135</v>
+        <v>21330051920328</v>
       </c>
       <c r="B35" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="D35" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="E35" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F35" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>22330051920129</v>
-      </c>
-      <c r="B36" t="s">
-        <v>51</v>
-      </c>
-      <c r="C36" t="s">
-        <v>84</v>
-      </c>
-      <c r="D36" t="s">
-        <v>126</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>14</v>
-      </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>22330051920350</v>
-      </c>
-      <c r="B37" t="s">
-        <v>52</v>
-      </c>
-      <c r="C37" t="s">
-        <v>85</v>
-      </c>
-      <c r="D37" t="s">
-        <v>127</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>14</v>
-      </c>
-      <c r="G37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>22330051920138</v>
-      </c>
-      <c r="B38" t="s">
-        <v>53</v>
-      </c>
-      <c r="C38" t="s">
-        <v>86</v>
-      </c>
-      <c r="D38" t="s">
-        <v>128</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
-        <v>14</v>
-      </c>
-      <c r="G38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>22330051920110</v>
-      </c>
-      <c r="B39" t="s">
-        <v>54</v>
-      </c>
-      <c r="C39" t="s">
-        <v>73</v>
-      </c>
-      <c r="D39" t="s">
-        <v>129</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>14</v>
-      </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>22330051920140</v>
-      </c>
-      <c r="B40" t="s">
-        <v>55</v>
-      </c>
-      <c r="C40" t="s">
-        <v>87</v>
-      </c>
-      <c r="D40" t="s">
-        <v>130</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>14</v>
-      </c>
-      <c r="G40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>22330051920143</v>
-      </c>
-      <c r="B41" t="s">
-        <v>56</v>
-      </c>
-      <c r="C41" t="s">
-        <v>66</v>
-      </c>
-      <c r="D41" t="s">
-        <v>131</v>
-      </c>
-      <c r="E41" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" t="s">
-        <v>14</v>
-      </c>
-      <c r="G41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>22330051920145</v>
-      </c>
-      <c r="B42" t="s">
-        <v>57</v>
-      </c>
-      <c r="C42" t="s">
-        <v>88</v>
-      </c>
-      <c r="D42" t="s">
-        <v>132</v>
-      </c>
-      <c r="E42" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" t="s">
-        <v>14</v>
-      </c>
-      <c r="G42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>22330051920146</v>
-      </c>
-      <c r="B43" t="s">
-        <v>58</v>
-      </c>
-      <c r="C43" t="s">
-        <v>35</v>
-      </c>
-      <c r="D43" t="s">
-        <v>133</v>
-      </c>
-      <c r="E43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" t="s">
-        <v>14</v>
-      </c>
-      <c r="G43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>22330051920172</v>
-      </c>
-      <c r="B44" t="s">
-        <v>59</v>
-      </c>
-      <c r="C44" t="s">
-        <v>89</v>
-      </c>
-      <c r="D44" t="s">
-        <v>111</v>
-      </c>
-      <c r="E44" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" t="s">
-        <v>15</v>
-      </c>
-      <c r="G44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <v>21330051920298</v>
-      </c>
-      <c r="B45" t="s">
-        <v>60</v>
-      </c>
-      <c r="C45" t="s">
-        <v>30</v>
-      </c>
-      <c r="D45" t="s">
-        <v>134</v>
-      </c>
-      <c r="E45" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" t="s">
-        <v>17</v>
-      </c>
-      <c r="G45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46">
-        <v>21330051920299</v>
-      </c>
-      <c r="B46" t="s">
-        <v>60</v>
-      </c>
-      <c r="C46" t="s">
-        <v>30</v>
-      </c>
-      <c r="D46" t="s">
-        <v>135</v>
-      </c>
-      <c r="E46" t="s">
-        <v>9</v>
-      </c>
-      <c r="F46" t="s">
-        <v>17</v>
-      </c>
-      <c r="G46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>21330051920337</v>
-      </c>
-      <c r="B47" t="s">
-        <v>61</v>
-      </c>
-      <c r="C47" t="s">
-        <v>90</v>
-      </c>
-      <c r="D47" t="s">
-        <v>136</v>
-      </c>
-      <c r="E47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" t="s">
-        <v>17</v>
-      </c>
-      <c r="G47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>20330051920235</v>
-      </c>
-      <c r="B48" t="s">
-        <v>62</v>
-      </c>
-      <c r="C48" t="s">
-        <v>66</v>
-      </c>
-      <c r="D48" t="s">
-        <v>137</v>
-      </c>
-      <c r="E48" t="s">
-        <v>9</v>
-      </c>
-      <c r="F48" t="s">
-        <v>17</v>
-      </c>
-      <c r="G48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49">
-        <v>21330051920321</v>
-      </c>
-      <c r="B49" t="s">
-        <v>44</v>
-      </c>
-      <c r="C49" t="s">
-        <v>39</v>
-      </c>
-      <c r="D49" t="s">
-        <v>138</v>
-      </c>
-      <c r="E49" t="s">
-        <v>9</v>
-      </c>
-      <c r="F49" t="s">
-        <v>17</v>
-      </c>
-      <c r="G49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50">
-        <v>21330051920326</v>
-      </c>
-      <c r="B50" t="s">
-        <v>63</v>
-      </c>
-      <c r="C50" t="s">
-        <v>68</v>
-      </c>
-      <c r="D50" t="s">
-        <v>139</v>
-      </c>
-      <c r="E50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" t="s">
-        <v>17</v>
-      </c>
-      <c r="G50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51">
-        <v>21330051920328</v>
-      </c>
-      <c r="B51" t="s">
-        <v>64</v>
-      </c>
-      <c r="C51" t="s">
-        <v>91</v>
-      </c>
-      <c r="D51" t="s">
-        <v>140</v>
-      </c>
-      <c r="E51" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" t="s">
-        <v>17</v>
-      </c>
-      <c r="G51">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20221.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="108">
   <si>
     <t>Mat</t>
   </si>
@@ -97,63 +97,66 @@
     <t>ROMERO</t>
   </si>
   <si>
-    <t>GIL</t>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
   </si>
   <si>
     <t>ORTIZ</t>
   </si>
   <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>JORGE</t>
+  </si>
+  <si>
+    <t>LARRACILLA</t>
   </si>
   <si>
     <t>SOLANO</t>
   </si>
   <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>LARRACILLA</t>
-  </si>
-  <si>
     <t>ROJAS</t>
   </si>
   <si>
@@ -175,57 +178,69 @@
     <t>GILES</t>
   </si>
   <si>
+    <t>AMAYO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>ZEPACTLE</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>MONGE</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>ROCETE</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>PRADO</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>ZEPACTLE</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>ROCETE</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>LLAVE</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>OSORIO</t>
   </si>
   <si>
@@ -235,76 +250,76 @@
     <t>SAUL AZAEL</t>
   </si>
   <si>
-    <t>JOSE RAUL</t>
+    <t>CARLOS YAEL</t>
+  </si>
+  <si>
+    <t>DYLAN</t>
+  </si>
+  <si>
+    <t>CAROLINA</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>OSMAR UZIEL</t>
+  </si>
+  <si>
+    <t>YULIET</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>GABAEL</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>ROGGER JUSEFH</t>
   </si>
   <si>
     <t>KARLA ABIGAIL</t>
   </si>
   <si>
-    <t>JARED ABRAHAM</t>
-  </si>
-  <si>
-    <t>JULIAN DAVID</t>
-  </si>
-  <si>
-    <t>CAROLINA</t>
-  </si>
-  <si>
-    <t>LUZ YAMILET</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>GUSTAVO KALEL</t>
-  </si>
-  <si>
-    <t>KAREN</t>
+    <t>JOSE EMMANUEL</t>
+  </si>
+  <si>
+    <t>LUIS FELIPE</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>ANETTE</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
   </si>
   <si>
     <t>KEVIN</t>
-  </si>
-  <si>
-    <t>YULIET</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>GABAEL</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>ROGGER JUSEFH</t>
-  </si>
-  <si>
-    <t>JOSE EMMANUEL</t>
-  </si>
-  <si>
-    <t>LUIS FELIPE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>ARANZA MARLENE</t>
-  </si>
-  <si>
-    <t>CRISTINA YAJANI</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
   </si>
   <si>
     <t>AMISADAI</t>
@@ -749,19 +764,19 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>8</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>67.73999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="H3">
         <v>7</v>
@@ -804,10 +819,10 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F5">
         <v>40</v>
@@ -816,7 +831,7 @@
         <v>90.91</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -830,19 +845,19 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G6">
-        <v>79.06999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -853,22 +868,22 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7">
-        <v>80.95</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -908,10 +923,10 @@
         <v>44</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F9">
         <v>31</v>
@@ -993,19 +1008,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>56.67</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1019,16 +1037,19 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>65</v>
+      </c>
+      <c r="H4">
+        <v>7.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1042,16 +1063,19 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>86.36</v>
+      </c>
+      <c r="H5">
+        <v>8.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1068,7 +1092,7 @@
         <v>43</v>
       </c>
       <c r="E6">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1085,13 +1109,13 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1111,16 +1135,19 @@
         <v>27</v>
       </c>
       <c r="D8">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="E8">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>88.89</v>
+      </c>
+      <c r="H8">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1137,7 +1164,7 @@
         <v>44</v>
       </c>
       <c r="E9">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1219,22 +1246,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>67.73999999999999</v>
+        <v>60</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1251,13 +1278,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>72.5</v>
+        <v>67.5</v>
       </c>
       <c r="H4">
         <v>6.9</v>
@@ -1274,19 +1301,19 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G5">
-        <v>90.91</v>
+        <v>86.36</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1300,19 +1327,19 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G6">
-        <v>79.06999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1323,22 +1350,22 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7">
-        <v>80.95</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1364,7 +1391,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1378,10 +1405,10 @@
         <v>44</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F9">
         <v>31</v>
@@ -1438,10 +1465,10 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1461,10 +1488,10 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1478,16 +1505,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920036</v>
+        <v>22330051920034</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1501,16 +1528,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920041</v>
+        <v>22330051920035</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1524,22 +1551,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920044</v>
+        <v>22330051920065</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1547,22 +1574,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920045</v>
+        <v>22330051920084</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1570,22 +1597,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920065</v>
+        <v>22330051920131</v>
       </c>
       <c r="B8" t="s">
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1593,22 +1620,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920069</v>
+        <v>22330051920247</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1616,22 +1643,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920084</v>
+        <v>22330051920382</v>
       </c>
       <c r="B10" t="s">
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1639,22 +1666,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920131</v>
+        <v>21330051920303</v>
       </c>
       <c r="B11" t="s">
         <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1662,22 +1689,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920346</v>
+        <v>21330051920316</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1685,114 +1712,114 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920247</v>
+        <v>22330051920003</v>
       </c>
       <c r="B13" t="s">
         <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920354</v>
+        <v>22330051920320</v>
       </c>
       <c r="B14" t="s">
         <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920303</v>
+        <v>22330051920321</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920316</v>
+        <v>22330051920039</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920003</v>
+        <v>22330051920041</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1800,22 +1827,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920320</v>
+        <v>22330051920046</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1823,22 +1850,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920321</v>
+        <v>22330051920053</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="D19" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1846,22 +1873,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920039</v>
+        <v>22330051920054</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1869,22 +1896,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920046</v>
+        <v>22330051920059</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1892,16 +1919,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920053</v>
+        <v>22330051920061</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1915,16 +1942,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920054</v>
+        <v>22330051920064</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1938,16 +1965,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920064</v>
+        <v>22330051920334</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D24" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1961,22 +1988,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920066</v>
+        <v>22330051920098</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D25" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1984,22 +2011,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920336</v>
+        <v>22330051920340</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D26" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2007,22 +2034,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920340</v>
+        <v>22330051920354</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D27" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2033,13 +2060,13 @@
         <v>22330051920172</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2056,13 +2083,13 @@
         <v>21330051920298</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D29" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
@@ -2079,13 +2106,13 @@
         <v>21330051920299</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D30" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
@@ -2102,13 +2129,13 @@
         <v>21330051920337</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D31" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
@@ -2125,13 +2152,13 @@
         <v>20330051920235</v>
       </c>
       <c r="B32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D32" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
@@ -2148,13 +2175,13 @@
         <v>21330051920321</v>
       </c>
       <c r="B33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C33" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D33" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
@@ -2171,13 +2198,13 @@
         <v>21330051920326</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C34" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="D34" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
@@ -2194,13 +2221,13 @@
         <v>21330051920328</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C35" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D35" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20221.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="114">
   <si>
     <t>Mat</t>
   </si>
@@ -91,81 +91,90 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>GALVEZ</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
+    <t>TELE</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>JORGE</t>
+  </si>
+  <si>
+    <t>LARRACILLA</t>
+  </si>
+  <si>
     <t>DIAZ</t>
   </si>
   <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>LARRACILLA</t>
-  </si>
-  <si>
     <t>SOLANO</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
     <t>DOLORES</t>
   </si>
   <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
@@ -181,60 +190,66 @@
     <t>AMAYO</t>
   </si>
   <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
+    <t>PRADO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>MEZA</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>ROCETE</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
     <t>ZEPACTLE</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>ROCETE</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
     <t>MALDONADO</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>ANGUIANO</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -244,6 +259,9 @@
     <t>OSORIO</t>
   </si>
   <si>
+    <t>ANGELO</t>
+  </si>
+  <si>
     <t>CRISTHIAN</t>
   </si>
   <si>
@@ -256,85 +274,85 @@
     <t>DYLAN</t>
   </si>
   <si>
-    <t>CAROLINA</t>
+    <t>JORGE IVAN</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
+    <t>MELANIE SOFIA</t>
   </si>
   <si>
     <t>JOSE MIGUEL</t>
   </si>
   <si>
+    <t>ANETTE</t>
+  </si>
+  <si>
+    <t>BETSABETH</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>GUSTAVO KALEL</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>ACSA FERNANDA</t>
+  </si>
+  <si>
+    <t>OSMAR UZIEL</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>ROGGER JUSEFH</t>
+  </si>
+  <si>
+    <t>KARLA ABIGAIL</t>
+  </si>
+  <si>
+    <t>JOSE EMMANUEL</t>
+  </si>
+  <si>
+    <t>LUIS FELIPE</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
     <t>ABRIL</t>
   </si>
   <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>OSMAR UZIEL</t>
-  </si>
-  <si>
-    <t>YULIET</t>
+    <t>KEVIN</t>
+  </si>
+  <si>
+    <t>RUFINA ISABEL</t>
   </si>
   <si>
     <t>LUIS ANGEL</t>
   </si>
   <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>GABAEL</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>ROGGER JUSEFH</t>
-  </si>
-  <si>
-    <t>KARLA ABIGAIL</t>
-  </si>
-  <si>
-    <t>JOSE EMMANUEL</t>
-  </si>
-  <si>
-    <t>LUIS FELIPE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ANETTE</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
-  </si>
-  <si>
     <t>AMISADAI</t>
   </si>
   <si>
-    <t>ZURISADAI</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
     <t>JOSE RAFAEL</t>
-  </si>
-  <si>
-    <t>ANA LAURA</t>
   </si>
   <si>
     <t>IVANNA DANIELA</t>
@@ -988,16 +1006,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>67.65000000000001</v>
+      </c>
+      <c r="H2">
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1011,16 +1032,16 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>56.67</v>
+        <v>60</v>
       </c>
       <c r="H3">
         <v>7</v>
@@ -1037,7 +1058,7 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>14</v>
@@ -1049,7 +1070,7 @@
         <v>65</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1063,7 +1084,7 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>6</v>
@@ -1075,7 +1096,7 @@
         <v>86.36</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1089,16 +1110,19 @@
         <v>43</v>
       </c>
       <c r="D6">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>74.42</v>
+      </c>
+      <c r="H6">
+        <v>7.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1112,16 +1136,19 @@
         <v>43</v>
       </c>
       <c r="D7">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>79.06999999999999</v>
+      </c>
+      <c r="H7">
+        <v>7.9</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1135,16 +1162,16 @@
         <v>27</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G8">
-        <v>88.89</v>
+        <v>100</v>
       </c>
       <c r="H8">
         <v>8.300000000000001</v>
@@ -1161,16 +1188,19 @@
         <v>44</v>
       </c>
       <c r="D9">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>79.55</v>
+      </c>
+      <c r="H9">
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -1226,16 +1256,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>73.53</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1278,16 +1308,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>67.5</v>
+        <v>65</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1330,16 +1360,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G6">
-        <v>81.40000000000001</v>
+        <v>74.42</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1356,16 +1386,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G7">
-        <v>81.40000000000001</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1408,16 +1438,16 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F9">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G9">
-        <v>70.45</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H9">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -1427,7 +1457,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1459,16 +1489,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920013</v>
+        <v>22330051920011</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1482,16 +1512,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920026</v>
+        <v>22330051920013</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1505,22 +1535,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920034</v>
+        <v>22330051920026</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1528,16 +1558,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920035</v>
+        <v>22330051920034</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1551,22 +1581,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920065</v>
+        <v>22330051920035</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1574,22 +1604,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920084</v>
+        <v>22330051920327</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1597,22 +1627,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920131</v>
+        <v>22330051920064</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1620,22 +1650,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920247</v>
+        <v>22330051920079</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1643,22 +1673,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920382</v>
+        <v>22330051920084</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1666,22 +1696,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920303</v>
+        <v>22330051920098</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1689,22 +1719,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920316</v>
+        <v>22330051920121</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1712,137 +1742,137 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920003</v>
+        <v>22330051920244</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920320</v>
+        <v>22330051920346</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920321</v>
+        <v>22330051920247</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D15" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920039</v>
+        <v>22330051920144</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920041</v>
+        <v>22330051920382</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920046</v>
+        <v>22330051920003</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1850,22 +1880,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920053</v>
+        <v>22330051920321</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1873,22 +1903,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920054</v>
+        <v>22330051920039</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1896,22 +1926,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920059</v>
+        <v>22330051920041</v>
       </c>
       <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
         <v>42</v>
       </c>
-      <c r="C21" t="s">
-        <v>63</v>
-      </c>
       <c r="D21" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1919,22 +1949,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920061</v>
+        <v>22330051920046</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D22" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1942,16 +1972,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920064</v>
+        <v>22330051920053</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="D23" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1965,16 +1995,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920334</v>
+        <v>22330051920054</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D24" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1988,22 +2018,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920098</v>
+        <v>22330051920059</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D25" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -2011,22 +2041,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920340</v>
+        <v>22330051920061</v>
       </c>
       <c r="B26" t="s">
         <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D26" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2034,22 +2064,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920354</v>
+        <v>22330051920334</v>
       </c>
       <c r="B27" t="s">
         <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D27" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2057,22 +2087,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920172</v>
+        <v>22330051920340</v>
       </c>
       <c r="B28" t="s">
         <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D28" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -2080,22 +2110,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>21330051920298</v>
+        <v>22330051920131</v>
       </c>
       <c r="B29" t="s">
         <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="D29" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -2103,22 +2133,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>21330051920299</v>
+        <v>22330051920354</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="D30" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -2126,22 +2156,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>21330051920337</v>
+        <v>22330051920384</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D31" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E31" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2149,22 +2179,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>20330051920235</v>
+        <v>22330051920172</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D32" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2172,16 +2202,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>21330051920321</v>
+        <v>21330051920298</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
@@ -2195,16 +2225,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>21330051920326</v>
+        <v>20330051920235</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D34" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
@@ -2218,16 +2248,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>21330051920328</v>
+        <v>21330051920326</v>
       </c>
       <c r="B35" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C35" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D35" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
@@ -2236,6 +2266,29 @@
         <v>17</v>
       </c>
       <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>21330051920328</v>
+      </c>
+      <c r="B36" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" t="s">
+        <v>79</v>
+      </c>
+      <c r="D36" t="s">
+        <v>113</v>
+      </c>
+      <c r="E36" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" t="s">
+        <v>17</v>
+      </c>
+      <c r="G36">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20221.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="116">
   <si>
     <t>Mat</t>
   </si>
@@ -94,6 +94,9 @@
     <t>CRUZ</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -260,6 +263,9 @@
   </si>
   <si>
     <t>ANGELO</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
   </si>
   <si>
     <t>CRISTHIAN</t>
@@ -1136,7 +1142,7 @@
         <v>43</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>9</v>
@@ -1148,7 +1154,7 @@
         <v>79.06999999999999</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1188,16 +1194,16 @@
         <v>44</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G9">
-        <v>79.55</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H9">
         <v>6.3</v>
@@ -1457,7 +1463,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1495,10 +1501,10 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1512,16 +1518,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920013</v>
+        <v>22330051920007</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1535,16 +1541,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920026</v>
+        <v>22330051920013</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1558,22 +1564,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920034</v>
+        <v>22330051920026</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1581,16 +1587,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920035</v>
+        <v>22330051920034</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1604,7 +1610,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920327</v>
+        <v>22330051920035</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
@@ -1613,7 +1619,7 @@
         <v>57</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1627,7 +1633,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920064</v>
+        <v>22330051920327</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
@@ -1636,13 +1642,13 @@
         <v>58</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1650,16 +1656,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920079</v>
+        <v>22330051920064</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1673,16 +1679,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920084</v>
+        <v>22330051920079</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1696,22 +1702,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920098</v>
+        <v>22330051920084</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
         <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1719,16 +1725,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920121</v>
+        <v>22330051920098</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1742,22 +1748,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920244</v>
+        <v>22330051920121</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1765,16 +1771,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920346</v>
+        <v>22330051920244</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
         <v>62</v>
       </c>
       <c r="D14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1788,16 +1794,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920247</v>
+        <v>22330051920346</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1811,16 +1817,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920144</v>
+        <v>22330051920247</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1834,7 +1840,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920382</v>
+        <v>22330051920144</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
@@ -1843,13 +1849,13 @@
         <v>64</v>
       </c>
       <c r="D17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1857,7 +1863,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920003</v>
+        <v>22330051920382</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
@@ -1866,21 +1872,21 @@
         <v>65</v>
       </c>
       <c r="D18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920321</v>
+        <v>22330051920003</v>
       </c>
       <c r="B19" t="s">
         <v>38</v>
@@ -1889,7 +1895,7 @@
         <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1903,22 +1909,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920039</v>
+        <v>22330051920321</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
         <v>67</v>
       </c>
       <c r="D20" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1926,16 +1932,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920041</v>
+        <v>22330051920039</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="D21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1949,16 +1955,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920046</v>
+        <v>22330051920041</v>
       </c>
       <c r="B22" t="s">
         <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D22" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1972,22 +1978,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920053</v>
+        <v>22330051920046</v>
       </c>
       <c r="B23" t="s">
         <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D23" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1995,16 +2001,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920054</v>
+        <v>22330051920053</v>
       </c>
       <c r="B24" t="s">
         <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="D24" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -2018,7 +2024,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920059</v>
+        <v>22330051920054</v>
       </c>
       <c r="B25" t="s">
         <v>43</v>
@@ -2027,7 +2033,7 @@
         <v>69</v>
       </c>
       <c r="D25" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -2041,7 +2047,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920061</v>
+        <v>22330051920059</v>
       </c>
       <c r="B26" t="s">
         <v>44</v>
@@ -2050,7 +2056,7 @@
         <v>70</v>
       </c>
       <c r="D26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -2064,7 +2070,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920334</v>
+        <v>22330051920061</v>
       </c>
       <c r="B27" t="s">
         <v>45</v>
@@ -2073,7 +2079,7 @@
         <v>71</v>
       </c>
       <c r="D27" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -2087,7 +2093,7 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920340</v>
+        <v>22330051920334</v>
       </c>
       <c r="B28" t="s">
         <v>46</v>
@@ -2096,13 +2102,13 @@
         <v>72</v>
       </c>
       <c r="D28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -2110,7 +2116,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920131</v>
+        <v>22330051920340</v>
       </c>
       <c r="B29" t="s">
         <v>47</v>
@@ -2119,13 +2125,13 @@
         <v>73</v>
       </c>
       <c r="D29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -2133,7 +2139,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920354</v>
+        <v>22330051920131</v>
       </c>
       <c r="B30" t="s">
         <v>48</v>
@@ -2142,7 +2148,7 @@
         <v>74</v>
       </c>
       <c r="D30" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -2156,7 +2162,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>22330051920384</v>
+        <v>22330051920354</v>
       </c>
       <c r="B31" t="s">
         <v>49</v>
@@ -2165,13 +2171,13 @@
         <v>75</v>
       </c>
       <c r="D31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2179,7 +2185,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>22330051920172</v>
+        <v>22330051920384</v>
       </c>
       <c r="B32" t="s">
         <v>50</v>
@@ -2188,7 +2194,7 @@
         <v>76</v>
       </c>
       <c r="D32" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -2202,22 +2208,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>21330051920298</v>
+        <v>22330051920172</v>
       </c>
       <c r="B33" t="s">
         <v>51</v>
       </c>
       <c r="C33" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="D33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E33" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2225,16 +2231,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>20330051920235</v>
+        <v>21330051920298</v>
       </c>
       <c r="B34" t="s">
         <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="D34" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
@@ -2248,7 +2254,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>21330051920326</v>
+        <v>20330051920235</v>
       </c>
       <c r="B35" t="s">
         <v>53</v>
@@ -2257,7 +2263,7 @@
         <v>78</v>
       </c>
       <c r="D35" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
@@ -2271,7 +2277,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>21330051920328</v>
+        <v>21330051920326</v>
       </c>
       <c r="B36" t="s">
         <v>54</v>
@@ -2280,7 +2286,7 @@
         <v>79</v>
       </c>
       <c r="D36" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E36" t="s">
         <v>9</v>
@@ -2289,6 +2295,29 @@
         <v>17</v>
       </c>
       <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>21330051920328</v>
+      </c>
+      <c r="B37" t="s">
+        <v>55</v>
+      </c>
+      <c r="C37" t="s">
+        <v>80</v>
+      </c>
+      <c r="D37" t="s">
+        <v>115</v>
+      </c>
+      <c r="E37" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" t="s">
+        <v>17</v>
+      </c>
+      <c r="G37">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20221.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20221.xlsx
@@ -274,46 +274,46 @@
     <t>SAUL AZAEL</t>
   </si>
   <si>
+    <t>DYLAN</t>
+  </si>
+  <si>
+    <t>JORGE IVAN</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
+    <t>MELANIE SOFIA</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>ANETTE</t>
+  </si>
+  <si>
+    <t>BETSABETH</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>GUSTAVO KALEL</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>ACSA FERNANDA</t>
+  </si>
+  <si>
+    <t>OSMAR UZIEL</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
     <t>CARLOS YAEL</t>
-  </si>
-  <si>
-    <t>DYLAN</t>
-  </si>
-  <si>
-    <t>JORGE IVAN</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>MELANIE SOFIA</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>ANETTE</t>
-  </si>
-  <si>
-    <t>BETSABETH</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>GUSTAVO KALEL</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>ACSA FERNANDA</t>
-  </si>
-  <si>
-    <t>OSMAR UZIEL</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
   </si>
   <si>
     <t>ROGGER JUSEFH</t>
@@ -1587,13 +1587,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920034</v>
+        <v>22330051920035</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="D6" t="s">
         <v>85</v>
@@ -1610,13 +1610,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920035</v>
+        <v>22330051920327</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
         <v>86</v>
@@ -1633,13 +1633,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920327</v>
+        <v>22330051920064</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
         <v>87</v>
@@ -1648,7 +1648,7 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1656,13 +1656,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920064</v>
+        <v>22330051920079</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
         <v>88</v>
@@ -1679,13 +1679,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920079</v>
+        <v>22330051920084</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
         <v>89</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920084</v>
+        <v>22330051920098</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D11" t="s">
         <v>90</v>
@@ -1717,7 +1717,7 @@
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1725,13 +1725,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920098</v>
+        <v>22330051920121</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
         <v>91</v>
@@ -1748,13 +1748,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920121</v>
+        <v>22330051920244</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
         <v>92</v>
@@ -1763,7 +1763,7 @@
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1771,13 +1771,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920244</v>
+        <v>22330051920346</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
         <v>93</v>
@@ -1794,13 +1794,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920346</v>
+        <v>22330051920247</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s">
         <v>94</v>
@@ -1817,13 +1817,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920247</v>
+        <v>22330051920144</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s">
         <v>95</v>
@@ -1840,13 +1840,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920144</v>
+        <v>22330051920382</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s">
         <v>96</v>
@@ -1855,7 +1855,7 @@
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1863,13 +1863,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920382</v>
+        <v>22330051920003</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
         <v>97</v>
@@ -1878,24 +1878,24 @@
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920003</v>
+        <v>22330051920321</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1909,22 +1909,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920321</v>
+        <v>22330051920034</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="D20" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G20">
         <v>1</v>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20221.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20221.xlsx
@@ -91,54 +91,54 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>TELE</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>TELE</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
     <t>ORTIZ</t>
   </si>
   <si>
@@ -187,42 +187,42 @@
     <t>TRUJILLO</t>
   </si>
   <si>
+    <t>AMAYO</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>PRADO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>MEZA</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>ROCETE</t>
+  </si>
+  <si>
     <t>GILES</t>
   </si>
   <si>
-    <t>AMAYO</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>MEZA</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>ROCETE</t>
-  </si>
-  <si>
     <t>ZEPEDA</t>
   </si>
   <si>
@@ -262,55 +262,55 @@
     <t>OSORIO</t>
   </si>
   <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>DYLAN</t>
+  </si>
+  <si>
+    <t>JORGE IVAN</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
+    <t>MELANIE SOFIA</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>ANETTE</t>
+  </si>
+  <si>
+    <t>BETSABETH</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>GUSTAVO KALEL</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>ACSA FERNANDA</t>
+  </si>
+  <si>
+    <t>OSMAR UZIEL</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
     <t>ANGELO</t>
   </si>
   <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
     <t>CRISTHIAN</t>
   </si>
   <si>
     <t>SAUL AZAEL</t>
-  </si>
-  <si>
-    <t>DYLAN</t>
-  </si>
-  <si>
-    <t>JORGE IVAN</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>MELANIE SOFIA</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>ANETTE</t>
-  </si>
-  <si>
-    <t>BETSABETH</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>GUSTAVO KALEL</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>ACSA FERNANDA</t>
-  </si>
-  <si>
-    <t>OSMAR UZIEL</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
   </si>
   <si>
     <t>CARLOS YAEL</t>
@@ -1495,13 +1495,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920011</v>
+        <v>22330051920007</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
         <v>81</v>
@@ -1518,13 +1518,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920007</v>
+        <v>22330051920035</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
         <v>82</v>
@@ -1533,7 +1533,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1541,13 +1541,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920013</v>
+        <v>22330051920327</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
         <v>83</v>
@@ -1556,7 +1556,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1564,13 +1564,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920026</v>
+        <v>22330051920064</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
         <v>84</v>
@@ -1579,7 +1579,7 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1587,13 +1587,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920035</v>
+        <v>22330051920079</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
         <v>85</v>
@@ -1602,7 +1602,7 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1610,13 +1610,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920327</v>
+        <v>22330051920084</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
         <v>86</v>
@@ -1625,7 +1625,7 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1633,13 +1633,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920064</v>
+        <v>22330051920098</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
         <v>87</v>
@@ -1648,7 +1648,7 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1656,13 +1656,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920079</v>
+        <v>22330051920121</v>
       </c>
       <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
         <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>44</v>
       </c>
       <c r="D9" t="s">
         <v>88</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1679,13 +1679,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920084</v>
+        <v>22330051920244</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D10" t="s">
         <v>89</v>
@@ -1694,7 +1694,7 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920098</v>
+        <v>22330051920346</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D11" t="s">
         <v>90</v>
@@ -1717,7 +1717,7 @@
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1725,13 +1725,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920121</v>
+        <v>22330051920247</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D12" t="s">
         <v>91</v>
@@ -1740,7 +1740,7 @@
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1748,13 +1748,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920244</v>
+        <v>22330051920144</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
         <v>92</v>
@@ -1771,13 +1771,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920346</v>
+        <v>22330051920382</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="s">
         <v>93</v>
@@ -1786,7 +1786,7 @@
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1794,13 +1794,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920247</v>
+        <v>22330051920003</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D15" t="s">
         <v>94</v>
@@ -1809,21 +1809,21 @@
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920144</v>
+        <v>22330051920011</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="D16" t="s">
         <v>95</v>
@@ -1832,21 +1832,21 @@
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920382</v>
+        <v>22330051920013</v>
       </c>
       <c r="B17" t="s">
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="D17" t="s">
         <v>96</v>
@@ -1855,15 +1855,15 @@
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920003</v>
+        <v>22330051920321</v>
       </c>
       <c r="B18" t="s">
         <v>38</v>
@@ -1872,7 +1872,7 @@
         <v>66</v>
       </c>
       <c r="D18" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1886,7 +1886,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920321</v>
+        <v>22330051920026</v>
       </c>
       <c r="B19" t="s">
         <v>39</v>
@@ -1895,7 +1895,7 @@
         <v>67</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1912,7 +1912,7 @@
         <v>22330051920034</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
         <v>41</v>
@@ -1935,7 +1935,7 @@
         <v>22330051920039</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C21" t="s">
         <v>68</v>
@@ -2237,7 +2237,7 @@
         <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D34" t="s">
         <v>112</v>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20221.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20221.xlsx
@@ -1453,7 +1453,7 @@
         <v>81.81999999999999</v>
       </c>
       <c r="H9">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20221.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="120">
   <si>
     <t>Mat</t>
   </si>
@@ -94,6 +94,12 @@
     <t>CARRERA</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
     <t>GALVEZ</t>
   </si>
   <si>
@@ -124,6 +130,9 @@
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
     <t>APALE</t>
   </si>
   <si>
@@ -151,9 +160,6 @@
     <t>BAUTISTA</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -184,7 +190,10 @@
     <t>SOLIS</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>MORA</t>
   </si>
   <si>
     <t>AMAYO</t>
@@ -193,9 +202,6 @@
     <t>CONTRERAS</t>
   </si>
   <si>
-    <t>MORA</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
@@ -214,6 +220,9 @@
     <t>ZARATE</t>
   </si>
   <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
     <t>TEXOCO</t>
   </si>
   <si>
@@ -259,12 +268,15 @@
     <t>RAMOS</t>
   </si>
   <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
     <t>ANA KAREN</t>
   </si>
   <si>
+    <t>DIEGO JESUS</t>
+  </si>
+  <si>
+    <t>EIDAN JOSEPH</t>
+  </si>
+  <si>
     <t>DYLAN</t>
   </si>
   <si>
@@ -301,6 +313,9 @@
     <t>OSMAR UZIEL</t>
   </si>
   <si>
+    <t>KARINA YOSELIN</t>
+  </si>
+  <si>
     <t>DANIEL</t>
   </si>
   <si>
@@ -362,9 +377,6 @@
   </si>
   <si>
     <t>IVANNA DANIELA</t>
-  </si>
-  <si>
-    <t>KARINA YOSELIN</t>
   </si>
 </sst>
 </file>
@@ -1463,7 +1475,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1501,10 +1513,10 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1518,22 +1530,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920035</v>
+        <v>22330051920015</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1541,22 +1553,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920327</v>
+        <v>22330051920028</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1564,22 +1576,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920064</v>
+        <v>22330051920035</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1587,22 +1599,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920079</v>
+        <v>22330051920327</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1610,16 +1622,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920084</v>
+        <v>22330051920064</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1633,22 +1645,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920098</v>
+        <v>22330051920079</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1656,22 +1668,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920121</v>
+        <v>22330051920084</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1679,22 +1691,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920244</v>
+        <v>22330051920098</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1702,22 +1714,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920346</v>
+        <v>22330051920121</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1725,16 +1737,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920247</v>
+        <v>22330051920244</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1748,16 +1760,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920144</v>
+        <v>22330051920346</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1771,22 +1783,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920382</v>
+        <v>22330051920247</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1794,7 +1806,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920003</v>
+        <v>22330051920144</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
@@ -1803,76 +1815,76 @@
         <v>65</v>
       </c>
       <c r="D15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920011</v>
+        <v>22330051920382</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="D16" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920013</v>
+        <v>21330051920328</v>
       </c>
       <c r="B17" t="s">
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920321</v>
+        <v>22330051920003</v>
       </c>
       <c r="B18" t="s">
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D18" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1886,16 +1898,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920026</v>
+        <v>22330051920011</v>
       </c>
       <c r="B19" t="s">
         <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="D19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1909,22 +1921,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920034</v>
+        <v>22330051920013</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D20" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1932,22 +1944,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920039</v>
+        <v>22330051920321</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D21" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1955,22 +1967,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920041</v>
+        <v>22330051920026</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="D22" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1978,16 +1990,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920046</v>
+        <v>22330051920034</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D23" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -2001,22 +2013,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920053</v>
+        <v>22330051920039</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="D24" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -2024,22 +2036,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920054</v>
+        <v>22330051920041</v>
       </c>
       <c r="B25" t="s">
         <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="D25" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -2047,22 +2059,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920059</v>
+        <v>22330051920046</v>
       </c>
       <c r="B26" t="s">
         <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D26" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2070,16 +2082,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920061</v>
+        <v>22330051920053</v>
       </c>
       <c r="B27" t="s">
         <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="D27" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -2093,7 +2105,7 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920334</v>
+        <v>22330051920054</v>
       </c>
       <c r="B28" t="s">
         <v>46</v>
@@ -2102,7 +2114,7 @@
         <v>72</v>
       </c>
       <c r="D28" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2116,22 +2128,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920340</v>
+        <v>22330051920059</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="C29" t="s">
         <v>73</v>
       </c>
       <c r="D29" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -2139,22 +2151,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920131</v>
+        <v>22330051920061</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C30" t="s">
         <v>74</v>
       </c>
       <c r="D30" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -2162,22 +2174,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>22330051920354</v>
+        <v>22330051920334</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
         <v>75</v>
       </c>
       <c r="D31" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2185,22 +2197,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>22330051920384</v>
+        <v>22330051920340</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C32" t="s">
         <v>76</v>
       </c>
       <c r="D32" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2208,22 +2220,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>22330051920172</v>
+        <v>22330051920131</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C33" t="s">
         <v>77</v>
       </c>
       <c r="D33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2231,22 +2243,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>21330051920298</v>
+        <v>22330051920354</v>
       </c>
       <c r="B34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="D34" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E34" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -2254,22 +2266,22 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>20330051920235</v>
+        <v>22330051920384</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C35" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E35" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -2277,22 +2289,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>21330051920326</v>
+        <v>22330051920172</v>
       </c>
       <c r="B36" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C36" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D36" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E36" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -2300,16 +2312,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>21330051920328</v>
+        <v>21330051920298</v>
       </c>
       <c r="B37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C37" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="D37" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E37" t="s">
         <v>9</v>
@@ -2318,6 +2330,52 @@
         <v>17</v>
       </c>
       <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>20330051920235</v>
+      </c>
+      <c r="B38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C38" t="s">
+        <v>81</v>
+      </c>
+      <c r="D38" t="s">
+        <v>118</v>
+      </c>
+      <c r="E38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" t="s">
+        <v>17</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>21330051920326</v>
+      </c>
+      <c r="B39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" t="s">
+        <v>82</v>
+      </c>
+      <c r="D39" t="s">
+        <v>119</v>
+      </c>
+      <c r="E39" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" t="s">
+        <v>17</v>
+      </c>
+      <c r="G39">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20221.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="122">
   <si>
     <t>Mat</t>
   </si>
@@ -115,6 +115,9 @@
     <t>VELAZQUEZ</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>TELE</t>
   </si>
   <si>
@@ -184,9 +187,6 @@
     <t>DOLORES</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>SOLIS</t>
   </si>
   <si>
@@ -208,6 +208,9 @@
     <t>PRADO</t>
   </si>
   <si>
+    <t>LUGO</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
@@ -293,6 +296,9 @@
   </si>
   <si>
     <t>ANETTE</t>
+  </si>
+  <si>
+    <t>ZAYRA</t>
   </si>
   <si>
     <t>BETSABETH</t>
@@ -1475,7 +1481,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1516,7 +1522,7 @@
         <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1539,7 +1545,7 @@
         <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1562,7 +1568,7 @@
         <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1585,7 +1591,7 @@
         <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1608,7 +1614,7 @@
         <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1631,7 +1637,7 @@
         <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1654,7 +1660,7 @@
         <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1677,7 +1683,7 @@
         <v>61</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1700,7 +1706,7 @@
         <v>62</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1714,16 +1720,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920121</v>
+        <v>22330051920100</v>
       </c>
       <c r="B11" t="s">
         <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1737,22 +1743,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920244</v>
+        <v>22330051920121</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1760,16 +1766,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920346</v>
+        <v>22330051920244</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
         <v>64</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1783,16 +1789,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920247</v>
+        <v>22330051920346</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1806,16 +1812,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920144</v>
+        <v>22330051920247</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1829,7 +1835,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920382</v>
+        <v>22330051920144</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
@@ -1838,13 +1844,13 @@
         <v>66</v>
       </c>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1852,7 +1858,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920328</v>
+        <v>22330051920382</v>
       </c>
       <c r="B17" t="s">
         <v>37</v>
@@ -1861,13 +1867,13 @@
         <v>67</v>
       </c>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1875,7 +1881,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920003</v>
+        <v>21330051920328</v>
       </c>
       <c r="B18" t="s">
         <v>38</v>
@@ -1884,30 +1890,30 @@
         <v>68</v>
       </c>
       <c r="D18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920011</v>
+        <v>22330051920003</v>
       </c>
       <c r="B19" t="s">
         <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="D19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1921,16 +1927,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920013</v>
+        <v>22330051920011</v>
       </c>
       <c r="B20" t="s">
         <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1944,16 +1950,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920321</v>
+        <v>22330051920013</v>
       </c>
       <c r="B21" t="s">
         <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D21" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1967,7 +1973,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920026</v>
+        <v>22330051920321</v>
       </c>
       <c r="B22" t="s">
         <v>42</v>
@@ -1976,7 +1982,7 @@
         <v>70</v>
       </c>
       <c r="D22" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1990,22 +1996,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920034</v>
+        <v>22330051920026</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="D23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -2013,16 +2019,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920039</v>
+        <v>22330051920034</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C24" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="D24" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -2036,16 +2042,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920041</v>
+        <v>22330051920039</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="D25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -2059,16 +2065,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920046</v>
+        <v>22330051920041</v>
       </c>
       <c r="B26" t="s">
         <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D26" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -2082,22 +2088,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920053</v>
+        <v>22330051920046</v>
       </c>
       <c r="B27" t="s">
         <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="D27" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2105,16 +2111,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920054</v>
+        <v>22330051920053</v>
       </c>
       <c r="B28" t="s">
         <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="D28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2128,16 +2134,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920059</v>
+        <v>22330051920054</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
         <v>73</v>
       </c>
       <c r="D29" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -2151,16 +2157,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920061</v>
+        <v>22330051920059</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="C30" t="s">
         <v>74</v>
       </c>
       <c r="D30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -2174,7 +2180,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>22330051920334</v>
+        <v>22330051920061</v>
       </c>
       <c r="B31" t="s">
         <v>48</v>
@@ -2183,7 +2189,7 @@
         <v>75</v>
       </c>
       <c r="D31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -2197,7 +2203,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>22330051920340</v>
+        <v>22330051920334</v>
       </c>
       <c r="B32" t="s">
         <v>49</v>
@@ -2206,13 +2212,13 @@
         <v>76</v>
       </c>
       <c r="D32" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2220,7 +2226,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>22330051920131</v>
+        <v>22330051920340</v>
       </c>
       <c r="B33" t="s">
         <v>50</v>
@@ -2229,13 +2235,13 @@
         <v>77</v>
       </c>
       <c r="D33" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2243,7 +2249,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>22330051920354</v>
+        <v>22330051920131</v>
       </c>
       <c r="B34" t="s">
         <v>51</v>
@@ -2252,7 +2258,7 @@
         <v>78</v>
       </c>
       <c r="D34" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2266,7 +2272,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>22330051920384</v>
+        <v>22330051920354</v>
       </c>
       <c r="B35" t="s">
         <v>52</v>
@@ -2275,13 +2281,13 @@
         <v>79</v>
       </c>
       <c r="D35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -2289,7 +2295,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>22330051920172</v>
+        <v>22330051920384</v>
       </c>
       <c r="B36" t="s">
         <v>53</v>
@@ -2298,7 +2304,7 @@
         <v>80</v>
       </c>
       <c r="D36" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -2312,22 +2318,22 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>21330051920298</v>
+        <v>22330051920172</v>
       </c>
       <c r="B37" t="s">
         <v>54</v>
       </c>
       <c r="C37" t="s">
-        <v>29</v>
+        <v>81</v>
       </c>
       <c r="D37" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -2335,16 +2341,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>20330051920235</v>
+        <v>21330051920298</v>
       </c>
       <c r="B38" t="s">
         <v>55</v>
       </c>
       <c r="C38" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="D38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E38" t="s">
         <v>9</v>
@@ -2358,16 +2364,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>21330051920326</v>
+        <v>20330051920235</v>
       </c>
       <c r="B39" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="C39" t="s">
         <v>82</v>
       </c>
       <c r="D39" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E39" t="s">
         <v>9</v>
@@ -2376,6 +2382,29 @@
         <v>17</v>
       </c>
       <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>21330051920326</v>
+      </c>
+      <c r="B40" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" t="s">
+        <v>121</v>
+      </c>
+      <c r="E40" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" t="s">
+        <v>17</v>
+      </c>
+      <c r="G40">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20221.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="110">
   <si>
     <t>Mat</t>
   </si>
@@ -91,115 +91,136 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>JORGE</t>
   </si>
   <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
+    <t>LARRACILLA</t>
   </si>
   <si>
     <t>TELE</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
+    <t>DOLORES</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
   </si>
   <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>LARRACILLA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>QUERO</t>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>LUGO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>MEZA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>ROCETE</t>
   </si>
   <si>
     <t>MORA</t>
   </si>
   <si>
-    <t>AMAYO</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
   </si>
   <si>
     <t>TEXCAHUA</t>
@@ -208,172 +229,115 @@
     <t>PRADO</t>
   </si>
   <si>
-    <t>LUGO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>MEZA</t>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>ZEPACTLE</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>VERA</t>
   </si>
   <si>
     <t>ZARATE</t>
   </si>
   <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>ROCETE</t>
-  </si>
-  <si>
-    <t>GILES</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>ZEPACTLE</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
     <t>RAMOS</t>
   </si>
   <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>JORGE IVAN</t>
+  </si>
+  <si>
+    <t>JIMENA</t>
+  </si>
+  <si>
+    <t>DANA PAOLA</t>
+  </si>
+  <si>
+    <t>MELANIE SOFIA</t>
+  </si>
+  <si>
+    <t>ZAYRA</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>GUSTAVO KALEL</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>ACSA FERNANDA</t>
+  </si>
+  <si>
+    <t>LUIS BRANDON</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>KARINA YOSELIN</t>
+  </si>
+  <si>
+    <t>ANGELO</t>
+  </si>
+  <si>
     <t>ANA KAREN</t>
   </si>
   <si>
-    <t>DIEGO JESUS</t>
-  </si>
-  <si>
     <t>EIDAN JOSEPH</t>
   </si>
   <si>
-    <t>DYLAN</t>
-  </si>
-  <si>
-    <t>JORGE IVAN</t>
+    <t>LUIS FELIPE</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
   </si>
   <si>
     <t>DANIEL ELEAZAR</t>
   </si>
   <si>
-    <t>MELANIE SOFIA</t>
-  </si>
-  <si>
     <t>JOSE MIGUEL</t>
   </si>
   <si>
     <t>ANETTE</t>
   </si>
   <si>
-    <t>ZAYRA</t>
+    <t>MONSERRAT</t>
   </si>
   <si>
     <t>BETSABETH</t>
   </si>
   <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>GUSTAVO KALEL</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>ACSA FERNANDA</t>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
+    <t>RUFINA ISABEL</t>
   </si>
   <si>
     <t>OSMAR UZIEL</t>
-  </si>
-  <si>
-    <t>KARINA YOSELIN</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>ANGELO</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>SAUL AZAEL</t>
-  </si>
-  <si>
-    <t>CARLOS YAEL</t>
-  </si>
-  <si>
-    <t>ROGGER JUSEFH</t>
-  </si>
-  <si>
-    <t>KARLA ABIGAIL</t>
-  </si>
-  <si>
-    <t>JOSE EMMANUEL</t>
-  </si>
-  <si>
-    <t>LUIS FELIPE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
-  </si>
-  <si>
-    <t>RUFINA ISABEL</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
   </si>
   <si>
     <t>AMISADAI</t>
@@ -1280,16 +1244,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>67.65000000000001</v>
+        <v>79.41</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1306,13 +1270,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H3">
         <v>6.9</v>
@@ -1481,7 +1445,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1513,16 +1477,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920007</v>
+        <v>22330051920010</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1536,22 +1500,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920015</v>
+        <v>22330051920327</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1559,22 +1523,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920028</v>
+        <v>22330051920068</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1582,22 +1546,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920035</v>
+        <v>22330051920071</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1605,22 +1569,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920327</v>
+        <v>22330051920079</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1628,22 +1592,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920064</v>
+        <v>22330051920100</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1651,22 +1615,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920079</v>
+        <v>22330051920105</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1674,22 +1638,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920084</v>
+        <v>22330051920244</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1697,22 +1661,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920098</v>
+        <v>22330051920346</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1720,22 +1684,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920100</v>
+        <v>22330051920247</v>
       </c>
       <c r="B11" t="s">
         <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1743,22 +1707,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920121</v>
+        <v>22330051920144</v>
       </c>
       <c r="B12" t="s">
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1766,22 +1730,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920244</v>
+        <v>22330051920161</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1789,22 +1753,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920346</v>
+        <v>22330051920172</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1812,22 +1776,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920247</v>
+        <v>21330051920328</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1835,85 +1799,85 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920144</v>
+        <v>22330051920011</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920382</v>
+        <v>22330051920007</v>
       </c>
       <c r="B17" t="s">
         <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="D17" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920328</v>
+        <v>22330051920321</v>
       </c>
       <c r="B18" t="s">
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D18" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920003</v>
+        <v>22330051920028</v>
       </c>
       <c r="B19" t="s">
         <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D19" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1927,22 +1891,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920011</v>
+        <v>22330051920053</v>
       </c>
       <c r="B20" t="s">
         <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D20" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1950,22 +1914,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920013</v>
+        <v>22330051920054</v>
       </c>
       <c r="B21" t="s">
         <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D21" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1973,22 +1937,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920321</v>
+        <v>22330051920059</v>
       </c>
       <c r="B22" t="s">
         <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1996,22 +1960,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920026</v>
+        <v>22330051920061</v>
       </c>
       <c r="B23" t="s">
         <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D23" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -2019,22 +1983,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920034</v>
+        <v>22330051920064</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="D24" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -2042,22 +2006,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920039</v>
+        <v>22330051920334</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D25" t="s">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -2065,22 +2029,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920041</v>
+        <v>22330051920084</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="D26" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2088,22 +2052,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920046</v>
+        <v>22330051920098</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="D27" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2111,22 +2075,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920053</v>
+        <v>22330051920340</v>
       </c>
       <c r="B28" t="s">
         <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="D28" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -2134,22 +2098,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920054</v>
+        <v>22330051920121</v>
       </c>
       <c r="B29" t="s">
         <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="D29" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -2157,22 +2121,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920059</v>
+        <v>22330051920131</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D30" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -2180,22 +2144,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>22330051920061</v>
+        <v>22330051920354</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D31" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2203,22 +2167,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>22330051920334</v>
+        <v>22330051920384</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D32" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2226,22 +2190,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>22330051920340</v>
+        <v>22330051920382</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D33" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2249,22 +2213,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>22330051920131</v>
+        <v>21330051920298</v>
       </c>
       <c r="B34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="D34" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E34" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F34" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -2272,22 +2236,22 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>22330051920354</v>
+        <v>20330051920235</v>
       </c>
       <c r="B35" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="C35" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D35" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="E35" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F35" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -2295,116 +2259,24 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>22330051920384</v>
+        <v>21330051920326</v>
       </c>
       <c r="B36" t="s">
         <v>53</v>
       </c>
       <c r="C36" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D36" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E36" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F36" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>22330051920172</v>
-      </c>
-      <c r="B37" t="s">
-        <v>54</v>
-      </c>
-      <c r="C37" t="s">
-        <v>81</v>
-      </c>
-      <c r="D37" t="s">
-        <v>118</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>15</v>
-      </c>
-      <c r="G37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>21330051920298</v>
-      </c>
-      <c r="B38" t="s">
-        <v>55</v>
-      </c>
-      <c r="C38" t="s">
-        <v>29</v>
-      </c>
-      <c r="D38" t="s">
-        <v>119</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s">
-        <v>17</v>
-      </c>
-      <c r="G38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>20330051920235</v>
-      </c>
-      <c r="B39" t="s">
-        <v>32</v>
-      </c>
-      <c r="C39" t="s">
-        <v>82</v>
-      </c>
-      <c r="D39" t="s">
-        <v>120</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>17</v>
-      </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>21330051920326</v>
-      </c>
-      <c r="B40" t="s">
-        <v>56</v>
-      </c>
-      <c r="C40" t="s">
-        <v>83</v>
-      </c>
-      <c r="D40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" t="s">
-        <v>17</v>
-      </c>
-      <c r="G40">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20221.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="96">
   <si>
     <t>Mat</t>
   </si>
@@ -103,27 +103,21 @@
     <t>MENDOZA</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
     <t>LUNA</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
@@ -139,9 +133,6 @@
     <t>SARMIENTO</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
@@ -154,18 +145,15 @@
     <t>JORGE</t>
   </si>
   <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
     <t>LARRACILLA</t>
   </si>
   <si>
-    <t>TELE</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
     <t>SOLANO</t>
   </si>
   <si>
@@ -175,12 +163,6 @@
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
     <t>COYOHUA</t>
   </si>
   <si>
@@ -196,12 +178,12 @@
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>MEZA</t>
-  </si>
-  <si>
     <t>ANTONIO</t>
   </si>
   <si>
+    <t>TEQUILIQUIHUA</t>
+  </si>
+  <si>
     <t>ANGUIANO</t>
   </si>
   <si>
@@ -220,21 +202,24 @@
     <t>PALACIOS</t>
   </si>
   <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>PRADO</t>
+    <t>DELGADO</t>
   </si>
   <si>
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>ZEPACTLE</t>
-  </si>
-  <si>
     <t>MALDONADO</t>
   </si>
   <si>
@@ -244,12 +229,6 @@
     <t>ZARATE</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>DIEGO</t>
   </si>
   <si>
@@ -262,30 +241,21 @@
     <t>DANA PAOLA</t>
   </si>
   <si>
-    <t>MELANIE SOFIA</t>
-  </si>
-  <si>
     <t>ZAYRA</t>
   </si>
   <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
     <t>ALEXIS</t>
   </si>
   <si>
-    <t>GUSTAVO KALEL</t>
-  </si>
-  <si>
     <t>KAREN</t>
   </si>
   <si>
-    <t>ACSA FERNANDA</t>
-  </si>
-  <si>
     <t>LUIS BRANDON</t>
   </si>
   <si>
+    <t>MARIAM</t>
+  </si>
+  <si>
     <t>LUIS ANGEL</t>
   </si>
   <si>
@@ -301,9 +271,6 @@
     <t>EIDAN JOSEPH</t>
   </si>
   <si>
-    <t>LUIS FELIPE</t>
-  </si>
-  <si>
     <t>FATIMA</t>
   </si>
   <si>
@@ -316,21 +283,21 @@
     <t>DANIEL ELEAZAR</t>
   </si>
   <si>
+    <t>MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>NICOLAS</t>
+  </si>
+  <si>
     <t>JOSE MIGUEL</t>
   </si>
   <si>
-    <t>ANETTE</t>
+    <t>DAMON</t>
   </si>
   <si>
     <t>MONSERRAT</t>
   </si>
   <si>
-    <t>BETSABETH</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
-  </si>
-  <si>
     <t>KEVIN</t>
   </si>
   <si>
@@ -338,15 +305,6 @@
   </si>
   <si>
     <t>OSMAR UZIEL</t>
-  </si>
-  <si>
-    <t>AMISADAI</t>
-  </si>
-  <si>
-    <t>JOSE RAFAEL</t>
-  </si>
-  <si>
-    <t>IVANNA DANIELA</t>
   </si>
 </sst>
 </file>
@@ -1305,7 +1263,7 @@
         <v>65</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1322,16 +1280,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G5">
-        <v>86.36</v>
+        <v>90.91</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1348,16 +1306,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G6">
-        <v>74.42</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1374,16 +1332,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G7">
-        <v>79.06999999999999</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1409,7 +1367,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>8.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1426,16 +1384,16 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F9">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G9">
-        <v>81.81999999999999</v>
+        <v>88.64</v>
       </c>
       <c r="H9">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -1445,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1483,10 +1441,10 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1506,10 +1464,10 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1529,10 +1487,10 @@
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1552,10 +1510,10 @@
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1569,22 +1527,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920079</v>
+        <v>22330051920100</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1592,22 +1550,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920100</v>
+        <v>22330051920244</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1615,22 +1573,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920105</v>
+        <v>22330051920247</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1638,22 +1596,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920244</v>
+        <v>22330051920161</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1661,22 +1619,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920346</v>
+        <v>22330051920160</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1684,22 +1642,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920247</v>
+        <v>22330051920172</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1707,22 +1665,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920144</v>
+        <v>21330051920328</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1730,85 +1688,85 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920161</v>
+        <v>22330051920011</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920172</v>
+        <v>22330051920007</v>
       </c>
       <c r="B14" t="s">
         <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920328</v>
+        <v>22330051920321</v>
       </c>
       <c r="B15" t="s">
         <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920011</v>
+        <v>22330051920028</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1822,22 +1780,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920007</v>
+        <v>22330051920054</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1845,22 +1803,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920321</v>
+        <v>22330051920059</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1868,22 +1826,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920028</v>
+        <v>22330051920061</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="D19" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1891,16 +1849,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920053</v>
+        <v>22330051920064</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="D20" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1914,16 +1872,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920054</v>
+        <v>22330051920316</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D21" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1937,16 +1895,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920059</v>
+        <v>22330051920334</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D22" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1960,16 +1918,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920061</v>
+        <v>22330051920072</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D23" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1983,16 +1941,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920064</v>
+        <v>22330051920084</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
         <v>64</v>
       </c>
       <c r="D24" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -2006,22 +1964,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920334</v>
+        <v>22330051920337</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D25" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -2029,22 +1987,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920084</v>
+        <v>22330051920340</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D26" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2052,22 +2010,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920098</v>
+        <v>22330051920354</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2075,22 +2033,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920340</v>
+        <v>22330051920384</v>
       </c>
       <c r="B28" t="s">
         <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D28" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -2098,185 +2056,24 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920121</v>
+        <v>22330051920382</v>
       </c>
       <c r="B29" t="s">
         <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>22330051920131</v>
-      </c>
-      <c r="B30" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" t="s">
-        <v>71</v>
-      </c>
-      <c r="D30" t="s">
-        <v>103</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>14</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>22330051920354</v>
-      </c>
-      <c r="B31" t="s">
-        <v>49</v>
-      </c>
-      <c r="C31" t="s">
-        <v>72</v>
-      </c>
-      <c r="D31" t="s">
-        <v>104</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>14</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>22330051920384</v>
-      </c>
-      <c r="B32" t="s">
-        <v>50</v>
-      </c>
-      <c r="C32" t="s">
-        <v>73</v>
-      </c>
-      <c r="D32" t="s">
-        <v>105</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>15</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>22330051920382</v>
-      </c>
-      <c r="B33" t="s">
-        <v>51</v>
-      </c>
-      <c r="C33" t="s">
-        <v>74</v>
-      </c>
-      <c r="D33" t="s">
-        <v>106</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>15</v>
-      </c>
-      <c r="G33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>21330051920298</v>
-      </c>
-      <c r="B34" t="s">
-        <v>52</v>
-      </c>
-      <c r="C34" t="s">
-        <v>30</v>
-      </c>
-      <c r="D34" t="s">
-        <v>107</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>17</v>
-      </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>20330051920235</v>
-      </c>
-      <c r="B35" t="s">
-        <v>29</v>
-      </c>
-      <c r="C35" t="s">
-        <v>75</v>
-      </c>
-      <c r="D35" t="s">
-        <v>108</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>17</v>
-      </c>
-      <c r="G35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>21330051920326</v>
-      </c>
-      <c r="B36" t="s">
-        <v>53</v>
-      </c>
-      <c r="C36" t="s">
-        <v>76</v>
-      </c>
-      <c r="D36" t="s">
-        <v>109</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>17</v>
-      </c>
-      <c r="G36">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20221.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="99">
   <si>
     <t>Mat</t>
   </si>
@@ -106,54 +106,57 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>MAY</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>JORGE</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>LARRACILLA</t>
+  </si>
+  <si>
     <t>LUNA</t>
   </si>
   <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>LARRACILLA</t>
-  </si>
-  <si>
     <t>SOLANO</t>
   </si>
   <si>
@@ -175,51 +178,54 @@
     <t>LUGO</t>
   </si>
   <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>TEQUILIQUIHUA</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>ROCETE</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>DELGADO</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>TEQUILIQUIHUA</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>ROCETE</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>DELGADO</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
     <t>MALDONADO</t>
   </si>
   <si>
@@ -244,58 +250,61 @@
     <t>ZAYRA</t>
   </si>
   <si>
+    <t>GABRIELA AIMEE</t>
+  </si>
+  <si>
+    <t>LUIS BRANDON</t>
+  </si>
+  <si>
+    <t>MARIAM</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>KARINA YOSELIN</t>
+  </si>
+  <si>
+    <t>ANGELO</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
     <t>ALEXIS</t>
   </si>
   <si>
+    <t>EIDAN JOSEPH</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
+    <t>MARIA CECILIA</t>
+  </si>
+  <si>
+    <t>NICOLAS</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>DAMON</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
     <t>KAREN</t>
-  </si>
-  <si>
-    <t>LUIS BRANDON</t>
-  </si>
-  <si>
-    <t>MARIAM</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>KARINA YOSELIN</t>
-  </si>
-  <si>
-    <t>ANGELO</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>EIDAN JOSEPH</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>MARIA CECILIA</t>
-  </si>
-  <si>
-    <t>NICOLAS</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>DAMON</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
   </si>
   <si>
     <t>KEVIN</t>
@@ -1403,7 +1412,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1441,10 +1450,10 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1464,10 +1473,10 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1487,10 +1496,10 @@
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1510,10 +1519,10 @@
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1533,10 +1542,10 @@
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1550,16 +1559,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920244</v>
+        <v>22330051920136</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1573,22 +1582,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920247</v>
+        <v>22330051920161</v>
       </c>
       <c r="B8" t="s">
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1596,16 +1605,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920161</v>
+        <v>22330051920160</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1619,16 +1628,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920160</v>
+        <v>22330051920172</v>
       </c>
       <c r="B10" t="s">
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1642,22 +1651,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920172</v>
+        <v>21330051920328</v>
       </c>
       <c r="B11" t="s">
         <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1665,39 +1674,39 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920328</v>
+        <v>22330051920011</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920011</v>
+        <v>22330051920007</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1711,16 +1720,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920007</v>
+        <v>22330051920321</v>
       </c>
       <c r="B14" t="s">
         <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="D14" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1734,16 +1743,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920321</v>
+        <v>22330051920028</v>
       </c>
       <c r="B15" t="s">
         <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1757,22 +1766,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920028</v>
+        <v>22330051920054</v>
       </c>
       <c r="B16" t="s">
         <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1780,16 +1789,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920054</v>
+        <v>22330051920059</v>
       </c>
       <c r="B17" t="s">
         <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1803,16 +1812,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920059</v>
+        <v>22330051920061</v>
       </c>
       <c r="B18" t="s">
         <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1826,16 +1835,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920061</v>
+        <v>22330051920064</v>
       </c>
       <c r="B19" t="s">
         <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1849,16 +1858,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920064</v>
+        <v>22330051920316</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1872,16 +1881,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920316</v>
+        <v>22330051920334</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1895,16 +1904,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920334</v>
+        <v>22330051920072</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D22" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1918,16 +1927,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920072</v>
+        <v>22330051920084</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1941,22 +1950,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920084</v>
+        <v>22330051920337</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D24" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1964,16 +1973,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920337</v>
+        <v>22330051920340</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D25" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1987,22 +1996,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920340</v>
+        <v>22330051920244</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D26" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2010,16 +2019,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920354</v>
+        <v>22330051920247</v>
       </c>
       <c r="B27" t="s">
         <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D27" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -2033,22 +2042,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920384</v>
+        <v>22330051920354</v>
       </c>
       <c r="B28" t="s">
         <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -2056,16 +2065,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920382</v>
+        <v>22330051920384</v>
       </c>
       <c r="B29" t="s">
         <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D29" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -2074,6 +2083,29 @@
         <v>15</v>
       </c>
       <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>22330051920382</v>
+      </c>
+      <c r="B30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" t="s">
+        <v>98</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ochoa Martínez Mayeli - Estadisticos 20221.xlsx
+++ b/docentes/Ochoa Martínez Mayeli - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="99">
   <si>
     <t>Mat</t>
   </si>
@@ -94,123 +94,123 @@
     <t>CRUZ</t>
   </si>
   <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
     <t>MACHORRO</t>
   </si>
   <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MAY</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JORGE</t>
+  </si>
+  <si>
     <t>MENDOZA</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MAY</t>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>LARRACILLA</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
   </si>
   <si>
     <t>CONTRERAS</t>
   </si>
   <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>LARRACILLA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
     <t>COYOHUA</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>TEQUILIQUIHUA</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>ROCETE</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>LUGO</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>TEQUILIQUIHUA</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>ROCETE</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
@@ -223,9 +223,6 @@
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
     <t>MALDONADO</t>
   </si>
   <si>
@@ -238,79 +235,82 @@
     <t>DIEGO</t>
   </si>
   <si>
+    <t>JARED ABRAHAM</t>
+  </si>
+  <si>
+    <t>JULIAN DAVID</t>
+  </si>
+  <si>
+    <t>JIMENA</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>GABRIELA AIMEE</t>
+  </si>
+  <si>
+    <t>MARIAM</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>KARINA YOSELIN</t>
+  </si>
+  <si>
+    <t>ANGELO</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>EIDAN JOSEPH</t>
+  </si>
+  <si>
     <t>JORGE IVAN</t>
   </si>
   <si>
-    <t>JIMENA</t>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
+    <t>MARIA CECILIA</t>
   </si>
   <si>
     <t>DANA PAOLA</t>
   </si>
   <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
-    <t>GABRIELA AIMEE</t>
+    <t>NICOLAS</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>DAMON</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
+    <t>RUFINA ISABEL</t>
   </si>
   <si>
     <t>LUIS BRANDON</t>
-  </si>
-  <si>
-    <t>MARIAM</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>KARINA YOSELIN</t>
-  </si>
-  <si>
-    <t>ANGELO</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>EIDAN JOSEPH</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>MARIA CECILIA</t>
-  </si>
-  <si>
-    <t>NICOLAS</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>DAMON</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
-  </si>
-  <si>
-    <t>RUFINA ISABEL</t>
   </si>
   <si>
     <t>OSMAR UZIEL</t>
@@ -1412,7 +1412,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1453,7 +1453,7 @@
         <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1467,16 +1467,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920327</v>
+        <v>22330051920044</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1490,22 +1490,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920068</v>
+        <v>22330051920045</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1513,7 +1513,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920071</v>
+        <v>22330051920068</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
@@ -1522,7 +1522,7 @@
         <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920100</v>
+        <v>22330051920247</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
@@ -1545,13 +1545,13 @@
         <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1568,7 +1568,7 @@
         <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1582,7 +1582,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920161</v>
+        <v>22330051920160</v>
       </c>
       <c r="B8" t="s">
         <v>30</v>
@@ -1591,7 +1591,7 @@
         <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920160</v>
+        <v>22330051920172</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
@@ -1614,7 +1614,7 @@
         <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1628,7 +1628,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920172</v>
+        <v>21330051920328</v>
       </c>
       <c r="B10" t="s">
         <v>32</v>
@@ -1637,13 +1637,13 @@
         <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1651,39 +1651,39 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920328</v>
+        <v>22330051920011</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920011</v>
+        <v>22330051920007</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1697,16 +1697,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920007</v>
+        <v>22330051920321</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1720,7 +1720,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920321</v>
+        <v>22330051920028</v>
       </c>
       <c r="B14" t="s">
         <v>35</v>
@@ -1729,7 +1729,7 @@
         <v>58</v>
       </c>
       <c r="D14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920028</v>
+        <v>22330051920327</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1769,13 +1769,13 @@
         <v>22330051920054</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1792,13 +1792,13 @@
         <v>22330051920059</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1815,13 +1815,13 @@
         <v>22330051920061</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1838,13 +1838,13 @@
         <v>22330051920064</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1861,13 +1861,13 @@
         <v>22330051920316</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1884,13 +1884,13 @@
         <v>22330051920334</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1904,16 +1904,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920072</v>
+        <v>22330051920071</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1927,16 +1927,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920084</v>
+        <v>22330051920072</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1950,22 +1950,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920337</v>
+        <v>22330051920084</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1973,16 +1973,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920340</v>
+        <v>22330051920337</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1996,22 +1996,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920244</v>
+        <v>22330051920340</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D26" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2019,16 +2019,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920247</v>
+        <v>22330051920244</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C27" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="D27" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -2045,13 +2045,13 @@
         <v>22330051920354</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2068,13 +2068,13 @@
         <v>22330051920384</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -2088,16 +2088,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>22330051920382</v>
+        <v>22330051920161</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D30" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -2106,6 +2106,29 @@
         <v>15</v>
       </c>
       <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>22330051920382</v>
+      </c>
+      <c r="B31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" t="s">
+        <v>70</v>
+      </c>
+      <c r="D31" t="s">
+        <v>98</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31">
         <v>1</v>
       </c>
     </row>
